--- a/TagX_Financial_Model.xlsx
+++ b/TagX_Financial_Model.xlsx
@@ -1,26 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC230C3D-D032-3C45-A417-63B6B187D1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Dashboard" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Funding Required" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="B2C Revenue" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="B2B Revenue" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Revenue Summary" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="COGS Detail" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="OpEx" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="P&amp;L Statement" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Break-Even" state="visible" r:id="rId13"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="Assumptions" sheetId="2" r:id="rId2"/>
+    <sheet name="Funding Required" sheetId="3" r:id="rId3"/>
+    <sheet name="B2C Revenue" sheetId="4" r:id="rId4"/>
+    <sheet name="B2B Revenue" sheetId="5" r:id="rId5"/>
+    <sheet name="Revenue Summary" sheetId="6" r:id="rId6"/>
+    <sheet name="COGS Detail" sheetId="7" r:id="rId7"/>
+    <sheet name="OpEx" sheetId="8" r:id="rId8"/>
+    <sheet name="P&amp;L Statement" sheetId="9" r:id="rId9"/>
+    <sheet name="Break-Even" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="274">
   <si>
     <t>KEY METRIC</t>
   </si>
@@ -238,7 +242,7 @@
     <t>Team Salaries (₹/year)</t>
   </si>
   <si>
-    <t>2→4→6→10→15 people incl founders</t>
+    <t>2→4→5→10→15 people incl founders</t>
   </si>
   <si>
     <t>R&amp;D / Prototyping (₹/year)</t>
@@ -682,10 +686,10 @@
     <t>Selling Price per Tag (₹)</t>
   </si>
   <si>
-    <t>3000→3500→4500</t>
-  </si>
-  <si>
-    <t>₹3,000 intro, ₹3,500 Y3, ₹4,500 Y5</t>
+    <t>2699→3199→3999</t>
+  </si>
+  <si>
+    <t>₹2699 intro, ₹3199 Y3, ₹3999 Y5</t>
   </si>
   <si>
     <t>COGS per Tag (BOM + Assembly)</t>
@@ -709,7 +713,7 @@
     <t>Gross Profit per Tag (₹)</t>
   </si>
   <si>
-    <t>~71% margin</t>
+    <t>~67% margin</t>
   </si>
   <si>
     <t>Monthly Fixed Costs (Y1 est.)</t>
@@ -769,13 +773,13 @@
     <t>Year 4 (2029) — BREAK-EVEN ✓</t>
   </si>
   <si>
-    <t>EBITDA +₹103.0L, Net Income +₹74.3L. Profitable.</t>
+    <t>EBITDA +₹61.4L, Net Income +₹43.1L. Profitable.</t>
   </si>
   <si>
     <t>Year 5 (2030)</t>
   </si>
   <si>
-    <t>₹3.88Cr cumulative profit. Scaling aggressively.</t>
+    <t>₹2.70Cr cumulative profit. Scaling aggressively.</t>
   </si>
   <si>
     <t>── CUMULATIVE ──</t>
@@ -847,42 +851,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="₹#,##0"/>
+    <numFmt numFmtId="164" formatCode="\₹#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font/>
-    <font>
-      <b/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -904,12 +920,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
+        <fgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -942,14 +958,14 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -960,11 +976,11 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1308,15 +1324,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1336,47 +1352,47 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>828438</v>
+        <v>829828</v>
       </c>
       <c r="C2" s="3">
-        <v>1958869</v>
+        <v>2104543</v>
       </c>
       <c r="D2" s="3">
-        <v>5219749</v>
+        <v>6530934</v>
       </c>
       <c r="E2" s="3">
-        <v>22064248</v>
+        <v>17789248</v>
       </c>
       <c r="F2" s="3">
-        <v>71287120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56815570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="C3" s="4">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4">
-        <v>52.2</v>
+        <v>65.3</v>
       </c>
       <c r="E3" s="4">
-        <v>220.6</v>
+        <v>177.9</v>
       </c>
       <c r="F3" s="4">
-        <v>712.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>568.20000000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1384,19 +1400,19 @@
         <v>0.08</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D4" s="4">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="E4" s="4">
-        <v>2.21</v>
+        <v>1.78</v>
       </c>
       <c r="F4" s="4">
-        <v>7.13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1407,7 +1423,7 @@
         <v>500</v>
       </c>
       <c r="D5" s="4">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E5" s="4">
         <v>3000</v>
@@ -1416,15 +1432,15 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4">
         <v>30</v>
@@ -1433,10 +1449,10 @@
         <v>100</v>
       </c>
       <c r="F6" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1447,36 +1463,36 @@
         <v>850</v>
       </c>
       <c r="D7" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E7" s="4">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="4">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E8" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F8" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +1503,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4">
         <v>10</v>
@@ -1496,147 +1512,123 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>606156</v>
+        <v>604048</v>
       </c>
       <c r="C11" s="3">
-        <v>1538717</v>
+        <v>1682176</v>
       </c>
       <c r="D11" s="3">
-        <v>4430548</v>
+        <v>5514933</v>
       </c>
       <c r="E11" s="3">
-        <v>19802083</v>
+        <v>15527083</v>
       </c>
       <c r="F11" s="3">
-        <v>64111720</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49686370</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7">
-        <v>0.731685412788887</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.7855129669212183</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.848804798851439</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.8974737321661722</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.8993450710310642</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>0.72791952067175369</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.79930702294987555</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.84443251149069953</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.87283526543674017</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.8745203119496997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>637000</v>
+        <v>639010</v>
       </c>
       <c r="C13" s="3">
-        <v>2297800</v>
+        <v>2280500</v>
       </c>
       <c r="D13" s="3">
-        <v>5362500</v>
+        <v>4730000</v>
       </c>
       <c r="E13" s="3">
-        <v>9505000</v>
+        <v>9390000</v>
       </c>
       <c r="F13" s="3">
-        <v>16780000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+        <v>16380000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>-30844</v>
+        <v>-34962</v>
       </c>
       <c r="C14" s="3">
-        <v>-759083</v>
-      </c>
-      <c r="D14" s="3">
-        <v>-931952</v>
-      </c>
-      <c r="E14" s="8">
-        <v>10297083</v>
-      </c>
-      <c r="F14" s="8">
-        <v>47331720</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-598324</v>
+      </c>
+      <c r="D14" s="7">
+        <v>784933</v>
+      </c>
+      <c r="E14" s="7">
+        <v>6137083</v>
+      </c>
+      <c r="F14" s="7">
+        <v>33306370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
-        <v>-0.037231512798785185</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-0.3875108544777624</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.1785434510356724</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.46668633347485944</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.6639589311505361</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>-4.2131622456701871E-2</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.28430115231667874</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.1201869441644947</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.34498833227801423</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.58621905931771867</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -1656,7 +1648,7 @@
         <v>467798</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
@@ -1676,28 +1668,28 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C19" s="3">
-        <v>-1439166</v>
+        <v>-1278407</v>
       </c>
       <c r="D19" s="3">
-        <v>-1620023</v>
+        <v>96862</v>
       </c>
       <c r="E19" s="3">
-        <v>9905556</v>
+        <v>5745556</v>
       </c>
       <c r="F19" s="3">
-        <v>46863922</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+        <v>32838572</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="3">
@@ -1707,132 +1699,121 @@
         <v>0</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>24216</v>
       </c>
       <c r="E20" s="3">
-        <v>2476389</v>
+        <v>1436389</v>
       </c>
       <c r="F20" s="3">
-        <v>11715981</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+        <v>8209643</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C21" s="3">
-        <v>-1439166</v>
-      </c>
-      <c r="D21" s="3">
-        <v>-1620023</v>
-      </c>
-      <c r="E21" s="8">
-        <v>7429167</v>
-      </c>
-      <c r="F21" s="8">
-        <v>35147941</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-1278407</v>
+      </c>
+      <c r="D21" s="7">
+        <v>72646</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4309167</v>
+      </c>
+      <c r="F21" s="7">
+        <v>24628929</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="7">
-        <v>-0.8681120373522219</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-0.7346923148000198</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.3103641573569917</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.3367061048262329</v>
-      </c>
-      <c r="F22" s="7">
-        <v>0.4930475659558136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="6">
+        <v>-0.87162038398318686</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-0.60745111884147773</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1.1123370715429064E-2</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.24223435414470584</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.43348907702589273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="3">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C24" s="3">
-        <v>-2158343</v>
+        <v>-2001702</v>
       </c>
       <c r="D24" s="3">
-        <v>-3778366</v>
+        <v>-1929056</v>
       </c>
       <c r="E24" s="3">
-        <v>3650801</v>
+        <v>2380111</v>
       </c>
       <c r="F24" s="3">
-        <v>38798742</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27009040</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="4">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C25" s="4">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="D25" s="4">
-        <v>8.7</v>
+        <v>13.1</v>
       </c>
       <c r="E25" s="4">
-        <v>22.1</v>
+        <v>17.8</v>
       </c>
       <c r="F25" s="4">
-        <v>47.5</v>
+        <v>37.9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D55"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="13" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>217</v>
       </c>
@@ -1846,13 +1827,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>218</v>
       </c>
       <c r="B3" t="s">
@@ -1865,7 +1846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>219</v>
       </c>
@@ -1879,7 +1860,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
         <v>222</v>
       </c>
@@ -1893,7 +1874,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
         <v>224</v>
       </c>
@@ -1907,7 +1888,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>227</v>
       </c>
@@ -1921,12 +1902,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B8" s="14">
-        <v>2120</v>
+        <v>1819</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>9</v>
@@ -1935,21 +1916,13 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="21">
-        <v>0</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>230</v>
       </c>
@@ -1963,7 +1936,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>233</v>
       </c>
@@ -1977,7 +1950,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>236</v>
       </c>
@@ -1991,22 +1964,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="21">
-        <v>0</v>
-      </c>
-      <c r="C13" s="21">
-        <v>0</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>238</v>
       </c>
       <c r="B14" t="s">
@@ -2019,7 +1984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
         <v>239</v>
       </c>
@@ -2033,12 +1998,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B16" s="14">
-        <v>828438</v>
+        <v>829828</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>9</v>
@@ -2047,12 +2012,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B17" s="14">
-        <v>-30844</v>
+        <v>-34962</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>9</v>
@@ -2061,12 +2026,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B18" s="14">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>9</v>
@@ -2075,21 +2040,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="21">
-        <v>0</v>
-      </c>
-      <c r="C19" s="21">
-        <v>0</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="20" t="s">
         <v>244</v>
       </c>
@@ -2103,12 +2060,12 @@
         <v>245</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B21" s="14">
-        <v>1958869</v>
+        <v>2104543</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>9</v>
@@ -2117,12 +2074,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B22" s="14">
-        <v>-759083</v>
+        <v>-598324</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>9</v>
@@ -2131,12 +2088,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B23" s="14">
-        <v>-1439166</v>
+        <v>-1278407</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>9</v>
@@ -2145,21 +2102,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="21">
-        <v>0</v>
-      </c>
-      <c r="C24" s="21">
-        <v>0</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="20" t="s">
         <v>246</v>
       </c>
@@ -2173,12 +2122,12 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B26" s="14">
-        <v>5219749</v>
+        <v>6530934</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>9</v>
@@ -2187,12 +2136,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B27" s="14">
-        <v>-931952</v>
+        <v>784933</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>9</v>
@@ -2201,12 +2150,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B28" s="14">
-        <v>-1620023</v>
+        <v>72646</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>9</v>
@@ -2215,21 +2164,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="21">
-        <v>0</v>
-      </c>
-      <c r="C29" s="21">
-        <v>0</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="22" t="s">
         <v>248</v>
       </c>
@@ -2243,12 +2184,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B31" s="14">
-        <v>22064248</v>
+        <v>17789248</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>9</v>
@@ -2257,12 +2198,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B32" s="14">
-        <v>10297083</v>
+        <v>6137083</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>9</v>
@@ -2271,12 +2212,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B33" s="14">
-        <v>7429167</v>
+        <v>4309167</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>9</v>
@@ -2285,21 +2226,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="21">
-        <v>0</v>
-      </c>
-      <c r="C34" s="21">
-        <v>0</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="20" t="s">
         <v>250</v>
       </c>
@@ -2313,12 +2246,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B36" s="14">
-        <v>71287120</v>
+        <v>56815570</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>9</v>
@@ -2327,12 +2260,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B37" s="14">
-        <v>47331720</v>
+        <v>33306370</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>9</v>
@@ -2341,12 +2274,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B38" s="14">
-        <v>35147941</v>
+        <v>24628929</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>9</v>
@@ -2355,22 +2288,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="21">
-        <v>0</v>
-      </c>
-      <c r="C39" s="21">
-        <v>0</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>252</v>
       </c>
       <c r="B40" t="s">
@@ -2383,12 +2308,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="20" t="s">
         <v>253</v>
       </c>
       <c r="B41" s="14">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>9</v>
@@ -2397,12 +2322,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
         <v>254</v>
       </c>
       <c r="B42" s="14">
-        <v>-2158343</v>
+        <v>-2001702</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>9</v>
@@ -2411,12 +2336,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="20" t="s">
         <v>255</v>
       </c>
       <c r="B43" s="14">
-        <v>-3778366</v>
+        <v>-1929056</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>9</v>
@@ -2425,12 +2350,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="20" t="s">
         <v>256</v>
       </c>
       <c r="B44" s="14">
-        <v>3650801</v>
+        <v>2380111</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>9</v>
@@ -2439,36 +2364,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="21">
-        <v>0</v>
-      </c>
-      <c r="C45" s="21">
-        <v>0</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="21">
-        <v>0</v>
-      </c>
-      <c r="C46" s="21">
-        <v>0</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="20"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="20"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>257</v>
       </c>
       <c r="B47" t="s">
@@ -2481,7 +2390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="20" t="s">
         <v>258</v>
       </c>
@@ -2495,7 +2404,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="20" t="s">
         <v>261</v>
       </c>
@@ -2509,7 +2418,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="20" t="s">
         <v>264</v>
       </c>
@@ -2523,22 +2432,14 @@
         <v>266</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="21">
-        <v>0</v>
-      </c>
-      <c r="C51" s="21">
-        <v>0</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="20"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
         <v>267</v>
       </c>
       <c r="B52" t="s">
@@ -2551,7 +2452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="20" t="s">
         <v>268</v>
       </c>
@@ -2565,7 +2466,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="20" t="s">
         <v>270</v>
       </c>
@@ -2579,7 +2480,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="20" t="s">
         <v>272</v>
       </c>
@@ -2595,21 +2496,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -2632,30 +2533,20 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
@@ -2666,7 +2557,7 @@
         <v>500</v>
       </c>
       <c r="D3" s="4">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E3" s="4">
         <v>3000</v>
@@ -2678,30 +2569,30 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>3000</v>
+        <v>2699</v>
       </c>
       <c r="C4" s="3">
-        <v>3200</v>
+        <v>2999</v>
       </c>
       <c r="D4" s="3">
-        <v>3500</v>
+        <v>3199</v>
       </c>
       <c r="E4" s="3">
-        <v>4000</v>
+        <v>3499</v>
       </c>
       <c r="F4" s="3">
-        <v>4500</v>
+        <v>3999</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>29</v>
       </c>
@@ -2712,30 +2603,30 @@
         <v>850</v>
       </c>
       <c r="D5" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E5" s="4">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="12">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="12">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D6" s="12">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E6" s="12">
         <v>0.4</v>
@@ -2747,7 +2638,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>33</v>
       </c>
@@ -2770,21 +2661,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="12">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C8" s="12">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D8" s="12">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="12">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="12">
         <v>0.4</v>
@@ -2793,7 +2684,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>37</v>
       </c>
@@ -2816,7 +2707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>39</v>
       </c>
@@ -2839,61 +2730,37 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="10"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4">
         <v>30</v>
@@ -2902,59 +2769,59 @@
         <v>100</v>
       </c>
       <c r="F13" s="4">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="3">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="C14" s="3">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="D14" s="3">
-        <v>4499</v>
+        <v>5499</v>
       </c>
       <c r="E14" s="3">
-        <v>4499</v>
+        <v>5999</v>
       </c>
       <c r="F14" s="3">
-        <v>4999</v>
+        <v>5999</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C15" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E15" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F15" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>47</v>
       </c>
@@ -2968,16 +2835,16 @@
         <v>699</v>
       </c>
       <c r="E16" s="3">
+        <v>699</v>
+      </c>
+      <c r="F16" s="3">
         <v>799</v>
-      </c>
-      <c r="F16" s="3">
-        <v>999</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>49</v>
       </c>
@@ -3000,7 +2867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>51</v>
       </c>
@@ -3023,7 +2890,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>53</v>
       </c>
@@ -3046,7 +2913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>54</v>
       </c>
@@ -3069,30 +2936,30 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B21" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="C21" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="D21" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="E21" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="F21" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>56</v>
       </c>
@@ -3115,53 +2982,29 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="10"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="4">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
       <c r="G24" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -3184,7 +3027,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>61</v>
       </c>
@@ -3207,7 +3050,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>63</v>
       </c>
@@ -3230,7 +3073,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>65</v>
       </c>
@@ -3253,7 +3096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
@@ -3276,7 +3119,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>68</v>
       </c>
@@ -3299,53 +3142,29 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="4">
-        <v>0</v>
-      </c>
-      <c r="C31" s="4">
-        <v>0</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="4">
-        <v>0</v>
-      </c>
-      <c r="C32" s="4">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4">
-        <v>0</v>
-      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
       <c r="G32" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
@@ -3356,7 +3175,7 @@
         <v>1400000</v>
       </c>
       <c r="D33" s="3">
-        <v>3600000</v>
+        <v>3000000</v>
       </c>
       <c r="E33" s="3">
         <v>6000000</v>
@@ -3368,7 +3187,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>73</v>
       </c>
@@ -3376,10 +3195,10 @@
         <v>100000</v>
       </c>
       <c r="C34" s="3">
+        <v>120000</v>
+      </c>
+      <c r="D34" s="3">
         <v>150000</v>
-      </c>
-      <c r="D34" s="3">
-        <v>200000</v>
       </c>
       <c r="E34" s="3">
         <v>250000</v>
@@ -3391,7 +3210,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>75</v>
       </c>
@@ -3414,7 +3233,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>77</v>
       </c>
@@ -3437,7 +3256,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>79</v>
       </c>
@@ -3460,12 +3279,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>81</v>
       </c>
       <c r="B38" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C38" s="3">
         <v>30000</v>
@@ -3483,7 +3302,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
         <v>83</v>
       </c>
@@ -3506,7 +3325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
         <v>84</v>
       </c>
@@ -3529,7 +3348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
         <v>85</v>
       </c>
@@ -3552,7 +3371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
         <v>86</v>
       </c>
@@ -3575,53 +3394,29 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="4">
-        <v>0</v>
-      </c>
-      <c r="C43" s="4">
-        <v>0</v>
-      </c>
-      <c r="D43" s="4">
-        <v>0</v>
-      </c>
-      <c r="E43" s="4">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4">
-        <v>0</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="10"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="4">
-        <v>0</v>
-      </c>
-      <c r="C44" s="4">
-        <v>0</v>
-      </c>
-      <c r="D44" s="4">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4">
-        <v>0</v>
-      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
       <c r="G44" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
         <v>89</v>
       </c>
@@ -3644,7 +3439,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
         <v>92</v>
       </c>
@@ -3667,7 +3462,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
         <v>94</v>
       </c>
@@ -3690,7 +3485,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
         <v>9</v>
       </c>
@@ -3713,7 +3508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>96</v>
       </c>
@@ -3738,21 +3533,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="13" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>98</v>
       </c>
@@ -3763,12 +3558,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>99</v>
       </c>
@@ -3779,7 +3574,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -3790,40 +3585,40 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>103</v>
       </c>
       <c r="B5" s="14">
-        <v>30844</v>
+        <v>34962</v>
       </c>
       <c r="C5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>105</v>
       </c>
       <c r="B6" s="14">
-        <v>759083</v>
+        <v>598324</v>
       </c>
       <c r="C6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>107</v>
       </c>
       <c r="B7" s="14">
-        <v>378993</v>
+        <v>363329</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3834,18 +3629,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>108</v>
       </c>
       <c r="B9" s="16">
-        <v>4168920</v>
+        <v>3996615</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3856,7 +3651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -3867,7 +3662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -3878,7 +3673,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -3889,7 +3684,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>115</v>
       </c>
@@ -3900,7 +3695,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>117</v>
       </c>
@@ -3911,7 +3706,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -3922,7 +3717,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -3933,29 +3728,29 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>103</v>
       </c>
       <c r="B18" s="14">
-        <v>30844</v>
+        <v>34962</v>
       </c>
       <c r="C18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>124</v>
       </c>
       <c r="B19" s="14">
-        <v>759083</v>
+        <v>598324</v>
       </c>
       <c r="C19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -3966,12 +3761,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>126</v>
       </c>
       <c r="B21" s="16">
-        <v>3789927</v>
+        <v>3633286</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>127</v>
@@ -3979,20 +3774,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
@@ -4012,7 +3807,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -4023,7 +3818,7 @@
         <v>500</v>
       </c>
       <c r="D2" s="4">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E2" s="4">
         <v>3000</v>
@@ -4032,67 +3827,55 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B3" s="3">
-        <v>3000</v>
+        <v>2699</v>
       </c>
       <c r="C3" s="3">
-        <v>3200</v>
+        <v>2999</v>
       </c>
       <c r="D3" s="3">
-        <v>3500</v>
+        <v>3199</v>
       </c>
       <c r="E3" s="3">
-        <v>4000</v>
+        <v>3499</v>
       </c>
       <c r="F3" s="3">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B4" s="3">
-        <v>750000</v>
+        <v>674750</v>
       </c>
       <c r="C4" s="3">
-        <v>1600000</v>
+        <v>1499500</v>
       </c>
       <c r="D4" s="3">
-        <v>3500000</v>
+        <v>4158700</v>
       </c>
       <c r="E4" s="3">
-        <v>12000000</v>
+        <v>10497000</v>
       </c>
       <c r="F4" s="3">
-        <v>45000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39990000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
@@ -4103,211 +3886,175 @@
         <v>850</v>
       </c>
       <c r="D6" s="4">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E6" s="4">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="4">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="B7" s="6">
         <v>0.25</v>
       </c>
-      <c r="E7" s="7">
+      <c r="C7" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="6">
         <v>0.4</v>
       </c>
-      <c r="F7" s="7">
+      <c r="E7" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="6">
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B8" s="3">
-        <v>17970</v>
+        <v>29950</v>
       </c>
       <c r="C8" s="3">
-        <v>101830</v>
+        <v>152745</v>
       </c>
       <c r="D8" s="3">
-        <v>499375</v>
+        <v>639200</v>
       </c>
       <c r="E8" s="3">
-        <v>3596400</v>
+        <v>1998000</v>
       </c>
       <c r="F8" s="3">
-        <v>8991000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4495500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="B10" s="6">
         <v>0.25</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="C10" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="3">
-        <v>29970</v>
+        <v>49950</v>
       </c>
       <c r="C11" s="3">
-        <v>127373</v>
+        <v>254745</v>
       </c>
       <c r="D11" s="3">
-        <v>750000</v>
+        <v>960000</v>
       </c>
       <c r="E11" s="3">
-        <v>4725000</v>
+        <v>3000000</v>
       </c>
       <c r="F11" s="3">
-        <v>12000000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B13" s="3">
-        <v>22500</v>
+        <v>20243</v>
       </c>
       <c r="C13" s="3">
-        <v>48000</v>
+        <v>44985</v>
       </c>
       <c r="D13" s="3">
-        <v>105000</v>
+        <v>166348</v>
       </c>
       <c r="E13" s="3">
-        <v>360000</v>
+        <v>419880</v>
       </c>
       <c r="F13" s="3">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+        <v>1999500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>135</v>
       </c>
       <c r="B15" s="3">
-        <v>820440</v>
+        <v>774893</v>
       </c>
       <c r="C15" s="3">
-        <v>1877203</v>
+        <v>1951975</v>
       </c>
       <c r="D15" s="3">
-        <v>4854375</v>
+        <v>5924248</v>
       </c>
       <c r="E15" s="3">
-        <v>20681400</v>
+        <v>15914880</v>
       </c>
       <c r="F15" s="3">
-        <v>67341000</v>
+        <v>52485000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
@@ -4327,15 +4074,15 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4">
         <v>30</v>
@@ -4344,51 +4091,39 @@
         <v>100</v>
       </c>
       <c r="F2" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>7998</v>
+        <v>24995</v>
       </c>
       <c r="C3" s="3">
-        <v>31992</v>
+        <v>49990</v>
       </c>
       <c r="D3" s="3">
-        <v>134970</v>
+        <v>164970</v>
       </c>
       <c r="E3" s="3">
-        <v>449900</v>
+        <v>599900</v>
       </c>
       <c r="F3" s="3">
-        <v>1249750</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+        <v>1199800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>137</v>
       </c>
       <c r="B5" s="4">
@@ -4407,8 +4142,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>138</v>
       </c>
       <c r="B6" s="3">
@@ -4427,67 +4162,55 @@
         <v>224985</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>139</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="D7" s="3">
-        <v>39998</v>
+        <v>49998</v>
       </c>
       <c r="E7" s="3">
-        <v>119994</v>
+        <v>149994</v>
       </c>
       <c r="F7" s="3">
-        <v>299985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+        <v>374985</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
         <v>140</v>
       </c>
       <c r="B9" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E9" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F9" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>47</v>
       </c>
@@ -4501,54 +4224,42 @@
         <v>699</v>
       </c>
       <c r="E10" s="3">
+        <v>699</v>
+      </c>
+      <c r="F10" s="3">
         <v>799</v>
       </c>
-      <c r="F10" s="3">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
         <v>141</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>29940</v>
       </c>
       <c r="C11" s="3">
-        <v>11976</v>
+        <v>59880</v>
       </c>
       <c r="D11" s="3">
-        <v>50328</v>
+        <v>251640</v>
       </c>
       <c r="E11" s="3">
-        <v>191760</v>
+        <v>503280</v>
       </c>
       <c r="F11" s="3">
-        <v>599400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+        <v>958800</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="4">
@@ -4567,7 +4278,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>51</v>
       </c>
@@ -4587,8 +4298,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B15" s="3">
@@ -4607,28 +4318,16 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="4">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B17" s="3">
@@ -4647,62 +4346,50 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="4">
-        <v>0</v>
-      </c>
-      <c r="C18" s="4">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>144</v>
       </c>
       <c r="B19" s="3">
-        <v>7998</v>
+        <v>54935</v>
       </c>
       <c r="C19" s="3">
-        <v>81666</v>
+        <v>152568</v>
       </c>
       <c r="D19" s="3">
-        <v>365374</v>
+        <v>606686</v>
       </c>
       <c r="E19" s="3">
-        <v>1382848</v>
+        <v>1874368</v>
       </c>
       <c r="F19" s="3">
-        <v>3946120</v>
+        <v>4330570</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -4722,108 +4409,108 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B2" s="3">
-        <v>750000</v>
+        <v>674750</v>
       </c>
       <c r="C2" s="3">
-        <v>1600000</v>
+        <v>1499500</v>
       </c>
       <c r="D2" s="3">
-        <v>3500000</v>
+        <v>4158700</v>
       </c>
       <c r="E2" s="3">
-        <v>12000000</v>
+        <v>10497000</v>
       </c>
       <c r="F2" s="3">
-        <v>45000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39990000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B3" s="3">
-        <v>17970</v>
+        <v>29950</v>
       </c>
       <c r="C3" s="3">
-        <v>101830</v>
+        <v>152745</v>
       </c>
       <c r="D3" s="3">
-        <v>499375</v>
+        <v>639200</v>
       </c>
       <c r="E3" s="3">
-        <v>3596400</v>
+        <v>1998000</v>
       </c>
       <c r="F3" s="3">
-        <v>8991000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4495500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B4" s="3">
-        <v>29970</v>
+        <v>49950</v>
       </c>
       <c r="C4" s="3">
-        <v>127373</v>
+        <v>254745</v>
       </c>
       <c r="D4" s="3">
-        <v>750000</v>
+        <v>960000</v>
       </c>
       <c r="E4" s="3">
-        <v>4725000</v>
+        <v>3000000</v>
       </c>
       <c r="F4" s="3">
-        <v>12000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B5" s="3">
-        <v>22500</v>
+        <v>20243</v>
       </c>
       <c r="C5" s="3">
-        <v>48000</v>
+        <v>44985</v>
       </c>
       <c r="D5" s="3">
-        <v>105000</v>
+        <v>166348</v>
       </c>
       <c r="E5" s="3">
-        <v>360000</v>
+        <v>419880</v>
       </c>
       <c r="F5" s="3">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1999500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B6" s="3">
-        <v>7998</v>
+        <v>24995</v>
       </c>
       <c r="C6" s="3">
-        <v>31992</v>
+        <v>49990</v>
       </c>
       <c r="D6" s="3">
-        <v>134970</v>
+        <v>164970</v>
       </c>
       <c r="E6" s="3">
-        <v>449900</v>
+        <v>599900</v>
       </c>
       <c r="F6" s="3">
-        <v>1249750</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+        <v>1199800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>151</v>
       </c>
       <c r="B7" s="3">
@@ -4842,48 +4529,48 @@
         <v>224985</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>152</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19999</v>
+        <v>24999</v>
       </c>
       <c r="D8" s="3">
-        <v>39998</v>
+        <v>49998</v>
       </c>
       <c r="E8" s="3">
-        <v>119994</v>
+        <v>149994</v>
       </c>
       <c r="F8" s="3">
-        <v>299985</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+        <v>374985</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>29940</v>
       </c>
       <c r="C9" s="3">
-        <v>11976</v>
+        <v>59880</v>
       </c>
       <c r="D9" s="3">
-        <v>50328</v>
+        <v>251640</v>
       </c>
       <c r="E9" s="3">
-        <v>191760</v>
+        <v>503280</v>
       </c>
       <c r="F9" s="3">
-        <v>599400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+        <v>958800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>154</v>
       </c>
       <c r="B10" s="3">
@@ -4902,8 +4589,8 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
         <v>155</v>
       </c>
       <c r="B11" s="3">
@@ -4922,87 +4609,63 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>156</v>
       </c>
       <c r="B13" s="3">
-        <v>828438</v>
+        <v>829828</v>
       </c>
       <c r="C13" s="3">
-        <v>1958869</v>
+        <v>2104543</v>
       </c>
       <c r="D13" s="3">
-        <v>5219749</v>
+        <v>6530934</v>
       </c>
       <c r="E13" s="3">
-        <v>22064248</v>
+        <v>17789248</v>
       </c>
       <c r="F13" s="3">
-        <v>71287120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56815570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="4">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="C15" s="4">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="D15" s="4">
-        <v>52.2</v>
+        <v>65.3</v>
       </c>
       <c r="E15" s="4">
-        <v>220.6</v>
+        <v>177.9</v>
       </c>
       <c r="F15" s="4">
-        <v>712.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>568.20000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -5010,114 +4673,102 @@
         <v>0.08</v>
       </c>
       <c r="C16" s="4">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D16" s="4">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="E16" s="4">
-        <v>2.21</v>
+        <v>1.78</v>
       </c>
       <c r="F16" s="4">
-        <v>7.13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
-      <c r="C17" s="4">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="7">
-        <v>0.99</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.958</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.937</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0.945</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="6">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0.92400000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="7">
-        <v>0.01</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.042</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.07</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.063</v>
-      </c>
-      <c r="F19" s="7">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="B19" s="6">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="C19" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="D19" s="6">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.105</v>
+      </c>
+      <c r="F19" s="6">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>0</v>
       </c>
-      <c r="C20" s="7">
-        <v>1.365</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.665</v>
-      </c>
-      <c r="E20" s="7">
-        <v>3.227</v>
-      </c>
-      <c r="F20" s="7">
-        <v>2.231</v>
+      <c r="C20" s="6">
+        <v>1.536</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2.1030000000000002</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.724</v>
+      </c>
+      <c r="F20" s="6">
+        <v>2.194</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>160</v>
       </c>
@@ -5137,27 +4788,17 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="19">
-        <v>0</v>
-      </c>
-      <c r="D2" s="19">
-        <v>0</v>
-      </c>
-      <c r="E2" s="19">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>129</v>
       </c>
@@ -5168,7 +4809,7 @@
         <v>500</v>
       </c>
       <c r="D3" s="4">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E3" s="4">
         <v>3000</v>
@@ -5177,7 +4818,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>162</v>
       </c>
@@ -5197,7 +4838,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>163</v>
       </c>
@@ -5217,7 +4858,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>164</v>
       </c>
@@ -5237,7 +4878,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>165</v>
       </c>
@@ -5248,7 +4889,7 @@
         <v>387500</v>
       </c>
       <c r="D7" s="3">
-        <v>720000</v>
+        <v>936000</v>
       </c>
       <c r="E7" s="3">
         <v>2055000</v>
@@ -5257,7 +4898,7 @@
         <v>6600000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>166</v>
       </c>
@@ -5268,7 +4909,7 @@
         <v>23250</v>
       </c>
       <c r="D8" s="3">
-        <v>36000</v>
+        <v>46800</v>
       </c>
       <c r="E8" s="3">
         <v>102750</v>
@@ -5277,7 +4918,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>167</v>
       </c>
@@ -5288,7 +4929,7 @@
         <v>410750</v>
       </c>
       <c r="D9" s="3">
-        <v>756000</v>
+        <v>982800</v>
       </c>
       <c r="E9" s="3">
         <v>2157750</v>
@@ -5297,55 +4938,33 @@
         <v>6930000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="19">
-        <v>0</v>
-      </c>
-      <c r="C11" s="19">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19">
-        <v>0</v>
-      </c>
-      <c r="E11" s="19">
-        <v>0</v>
-      </c>
-      <c r="F11" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>169</v>
       </c>
       <c r="B12" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="4">
         <v>30</v>
@@ -5354,10 +4973,10 @@
         <v>100</v>
       </c>
       <c r="F12" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>170</v>
       </c>
@@ -5377,7 +4996,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>171</v>
       </c>
@@ -5397,7 +5016,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>164</v>
       </c>
@@ -5417,15 +5036,15 @@
         <v>880</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B16" s="3">
-        <v>2200</v>
+        <v>5500</v>
       </c>
       <c r="C16" s="3">
-        <v>8360</v>
+        <v>10450</v>
       </c>
       <c r="D16" s="3">
         <v>29700</v>
@@ -5434,18 +5053,18 @@
         <v>93500</v>
       </c>
       <c r="F16" s="3">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>176000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B17" s="3">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="C17" s="3">
-        <v>502</v>
+        <v>627</v>
       </c>
       <c r="D17" s="3">
         <v>1485</v>
@@ -5454,18 +5073,18 @@
         <v>4675</v>
       </c>
       <c r="F17" s="3">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B18" s="3">
-        <v>2332</v>
+        <v>5830</v>
       </c>
       <c r="C18" s="3">
-        <v>8862</v>
+        <v>11077</v>
       </c>
       <c r="D18" s="3">
         <v>31185</v>
@@ -5474,10 +5093,10 @@
         <v>98175</v>
       </c>
       <c r="F18" s="3">
-        <v>231000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>184800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -5497,8 +5116,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>174</v>
       </c>
       <c r="B20" s="3">
@@ -5517,7 +5136,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -5537,87 +5156,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>175</v>
       </c>
       <c r="B22" s="3">
-        <v>222282</v>
+        <v>225780</v>
       </c>
       <c r="C22" s="3">
-        <v>420152</v>
+        <v>422367</v>
       </c>
       <c r="D22" s="3">
-        <v>789201</v>
+        <v>1016001</v>
       </c>
       <c r="E22" s="3">
         <v>2262165</v>
       </c>
       <c r="F22" s="3">
-        <v>7175400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7129200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B24" s="19">
-        <v>0</v>
-      </c>
-      <c r="C24" s="19">
-        <v>0</v>
-      </c>
-      <c r="D24" s="19">
-        <v>0</v>
-      </c>
-      <c r="E24" s="19">
-        <v>0</v>
-      </c>
-      <c r="F24" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B25" s="3">
-        <v>3000</v>
+        <v>2699</v>
       </c>
       <c r="C25" s="3">
-        <v>3200</v>
+        <v>2999</v>
       </c>
       <c r="D25" s="3">
-        <v>3500</v>
+        <v>3199</v>
       </c>
       <c r="E25" s="3">
-        <v>4000</v>
+        <v>3499</v>
       </c>
       <c r="F25" s="3">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>178</v>
       </c>
@@ -5637,47 +5234,47 @@
         <v>693</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>179</v>
       </c>
       <c r="B27" s="3">
-        <v>2120</v>
+        <v>1819</v>
       </c>
       <c r="C27" s="3">
-        <v>2378</v>
+        <v>2177</v>
       </c>
       <c r="D27" s="3">
-        <v>2744</v>
+        <v>2443</v>
       </c>
       <c r="E27" s="3">
-        <v>3281</v>
+        <v>2780</v>
       </c>
       <c r="F27" s="3">
-        <v>3807</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B28" s="7">
-        <v>0.707</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0.743</v>
-      </c>
-      <c r="D28" s="7">
-        <v>0.784</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.82</v>
-      </c>
-      <c r="F28" s="7">
-        <v>0.846</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="6">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.82699999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -5697,27 +5294,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B30" s="3">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="C30" s="3">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="D30" s="3">
-        <v>4499</v>
+        <v>5499</v>
       </c>
       <c r="E30" s="3">
-        <v>4499</v>
+        <v>5999</v>
       </c>
       <c r="F30" s="3">
-        <v>4999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>182</v>
       </c>
@@ -5737,62 +5334,62 @@
         <v>924</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>183</v>
       </c>
       <c r="B32" s="3">
-        <v>2833</v>
+        <v>3833</v>
       </c>
       <c r="C32" s="3">
-        <v>2891</v>
+        <v>3891</v>
       </c>
       <c r="D32" s="3">
-        <v>3459</v>
+        <v>4459</v>
       </c>
       <c r="E32" s="3">
-        <v>3517</v>
+        <v>5017</v>
       </c>
       <c r="F32" s="3">
-        <v>4075</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5075</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B33" s="7">
-        <v>0.708</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0.723</v>
-      </c>
-      <c r="D33" s="7">
-        <v>0.769</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.782</v>
-      </c>
-      <c r="F33" s="7">
-        <v>0.815</v>
+      <c r="B33" s="6">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0.84599999999999997</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>185</v>
       </c>
@@ -5812,7 +5409,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>186</v>
       </c>
@@ -5823,7 +5420,7 @@
         <v>1400000</v>
       </c>
       <c r="D2" s="3">
-        <v>3600000</v>
+        <v>3000000</v>
       </c>
       <c r="E2" s="3">
         <v>6000000</v>
@@ -5832,7 +5429,7 @@
         <v>9600000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>187</v>
       </c>
@@ -5840,10 +5437,10 @@
         <v>100000</v>
       </c>
       <c r="C3" s="3">
+        <v>120000</v>
+      </c>
+      <c r="D3" s="3">
         <v>150000</v>
-      </c>
-      <c r="D3" s="3">
-        <v>200000</v>
       </c>
       <c r="E3" s="3">
         <v>250000</v>
@@ -5852,7 +5449,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>188</v>
       </c>
@@ -5872,27 +5469,27 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>189</v>
       </c>
       <c r="B5" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C5" s="3">
-        <v>12800</v>
+        <v>25500</v>
       </c>
       <c r="D5" s="3">
-        <v>62500</v>
+        <v>80000</v>
       </c>
       <c r="E5" s="3">
-        <v>315000</v>
+        <v>200000</v>
       </c>
       <c r="F5" s="3">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>190</v>
       </c>
@@ -5912,12 +5509,12 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="C7" s="3">
         <v>30000</v>
@@ -5932,7 +5529,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>192</v>
       </c>
@@ -5952,7 +5549,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>193</v>
       </c>
@@ -5972,7 +5569,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>194</v>
       </c>
@@ -5992,8 +5589,8 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
         <v>195</v>
       </c>
       <c r="B11" s="3">
@@ -6012,102 +5609,78 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>196</v>
       </c>
       <c r="B13" s="3">
-        <v>637000</v>
+        <v>639010</v>
       </c>
       <c r="C13" s="3">
-        <v>2297800</v>
+        <v>2280500</v>
       </c>
       <c r="D13" s="3">
-        <v>5362500</v>
+        <v>4730000</v>
       </c>
       <c r="E13" s="3">
-        <v>9505000</v>
+        <v>9390000</v>
       </c>
       <c r="F13" s="3">
-        <v>16780000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16380000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="7">
-        <v>0.769</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.173</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.027</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.431</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.235</v>
+      <c r="B15" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.28799999999999998</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>198</v>
       </c>
@@ -6127,67 +5700,55 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B2" s="3">
-        <v>828438</v>
+        <v>829828</v>
       </c>
       <c r="C2" s="3">
-        <v>1958869</v>
+        <v>2104543</v>
       </c>
       <c r="D2" s="3">
-        <v>5219749</v>
+        <v>6530934</v>
       </c>
       <c r="E2" s="3">
-        <v>22064248</v>
+        <v>17789248</v>
       </c>
       <c r="F2" s="3">
-        <v>71287120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56815570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>200</v>
       </c>
       <c r="B4" s="3">
-        <v>222282</v>
+        <v>225780</v>
       </c>
       <c r="C4" s="3">
-        <v>420152</v>
+        <v>422367</v>
       </c>
       <c r="D4" s="3">
-        <v>789201</v>
+        <v>1016001</v>
       </c>
       <c r="E4" s="3">
         <v>2262165</v>
       </c>
       <c r="F4" s="3">
-        <v>7175400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7129200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>201</v>
       </c>
@@ -6198,7 +5759,7 @@
         <v>410750</v>
       </c>
       <c r="D5" s="3">
-        <v>756000</v>
+        <v>982800</v>
       </c>
       <c r="E5" s="3">
         <v>2157750</v>
@@ -6207,15 +5768,15 @@
         <v>6930000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>202</v>
       </c>
       <c r="B6" s="3">
-        <v>2332</v>
+        <v>5830</v>
       </c>
       <c r="C6" s="3">
-        <v>8862</v>
+        <v>11077</v>
       </c>
       <c r="D6" s="3">
         <v>31185</v>
@@ -6224,11 +5785,11 @@
         <v>98175</v>
       </c>
       <c r="F6" s="3">
-        <v>231000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+        <v>184800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>203</v>
       </c>
       <c r="B7" s="3">
@@ -6247,107 +5808,73 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>204</v>
       </c>
       <c r="B9" s="3">
-        <v>606156</v>
+        <v>604048</v>
       </c>
       <c r="C9" s="3">
-        <v>1538717</v>
+        <v>1682176</v>
       </c>
       <c r="D9" s="3">
-        <v>4430548</v>
+        <v>5514933</v>
       </c>
       <c r="E9" s="3">
-        <v>19802083</v>
+        <v>15527083</v>
       </c>
       <c r="F9" s="3">
-        <v>64111720</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49686370</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="7">
-        <v>0.731685412788887</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0.7855129669212183</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0.848804798851439</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.8974737321661722</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.8993450710310642</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="B10" s="6">
+        <v>0.72791952067175369</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.79930702294987555</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.84443251149069953</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.87283526543674017</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.8745203119496997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>206</v>
       </c>
@@ -6358,7 +5885,7 @@
         <v>1400000</v>
       </c>
       <c r="D13" s="3">
-        <v>3600000</v>
+        <v>3000000</v>
       </c>
       <c r="E13" s="3">
         <v>6000000</v>
@@ -6367,7 +5894,7 @@
         <v>9600000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>207</v>
       </c>
@@ -6375,10 +5902,10 @@
         <v>100000</v>
       </c>
       <c r="C14" s="3">
+        <v>120000</v>
+      </c>
+      <c r="D14" s="3">
         <v>150000</v>
-      </c>
-      <c r="D14" s="3">
-        <v>200000</v>
       </c>
       <c r="E14" s="3">
         <v>250000</v>
@@ -6387,7 +5914,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>208</v>
       </c>
@@ -6407,27 +5934,27 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>209</v>
       </c>
       <c r="B16" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C16" s="3">
-        <v>12800</v>
+        <v>25500</v>
       </c>
       <c r="D16" s="3">
-        <v>62500</v>
+        <v>80000</v>
       </c>
       <c r="E16" s="3">
-        <v>315000</v>
+        <v>200000</v>
       </c>
       <c r="F16" s="3">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>210</v>
       </c>
@@ -6447,12 +5974,12 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>211</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C18" s="3">
         <v>30000</v>
@@ -6467,7 +5994,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>212</v>
       </c>
@@ -6487,7 +6014,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>213</v>
       </c>
@@ -6507,7 +6034,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>214</v>
       </c>
@@ -6527,8 +6054,8 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
         <v>215</v>
       </c>
       <c r="B22" s="3">
@@ -6547,127 +6074,91 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="3">
-        <v>637000</v>
+        <v>639010</v>
       </c>
       <c r="C24" s="3">
-        <v>2297800</v>
+        <v>2280500</v>
       </c>
       <c r="D24" s="3">
-        <v>5362500</v>
+        <v>4730000</v>
       </c>
       <c r="E24" s="3">
-        <v>9505000</v>
+        <v>9390000</v>
       </c>
       <c r="F24" s="3">
-        <v>16780000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="4">
-        <v>0</v>
-      </c>
-      <c r="C25" s="4">
-        <v>0</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+        <v>16380000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="3">
-        <v>-30844</v>
+        <v>-34962</v>
       </c>
       <c r="C26" s="3">
-        <v>-759083</v>
-      </c>
-      <c r="D26" s="3">
-        <v>-931952</v>
-      </c>
-      <c r="E26" s="8">
-        <v>10297083</v>
-      </c>
-      <c r="F26" s="8">
-        <v>47331720</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-598324</v>
+      </c>
+      <c r="D26" s="7">
+        <v>784933</v>
+      </c>
+      <c r="E26" s="7">
+        <v>6137083</v>
+      </c>
+      <c r="F26" s="7">
+        <v>33306370</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="7">
-        <v>-0.037231512798785185</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-0.3875108544777624</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-0.1785434510356724</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.46668633347485944</v>
-      </c>
-      <c r="F27" s="7">
-        <v>0.6639589311505361</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="4">
-        <v>0</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="6">
+        <v>-4.2131622456701871E-2</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-0.28430115231667874</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.1201869441644947</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.34498833227801423</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0.58621905931771867</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>15</v>
       </c>
@@ -6687,48 +6178,36 @@
         <v>467798</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="3">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C30" s="3">
-        <v>-1439166</v>
+        <v>-1278407</v>
       </c>
       <c r="D30" s="3">
-        <v>-1620023</v>
+        <v>96862</v>
       </c>
       <c r="E30" s="3">
-        <v>9905556</v>
+        <v>5745556</v>
       </c>
       <c r="F30" s="3">
-        <v>46863922</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="4">
-        <v>0</v>
-      </c>
-      <c r="C31" s="4">
-        <v>0</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+        <v>32838572</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B32" s="3">
@@ -6738,97 +6217,85 @@
         <v>0</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>24216</v>
       </c>
       <c r="E32" s="3">
-        <v>2476389</v>
+        <v>1436389</v>
       </c>
       <c r="F32" s="3">
-        <v>11715981</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+        <v>8209643</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>216</v>
       </c>
       <c r="B33" s="3">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C33" s="3">
-        <v>-1439166</v>
-      </c>
-      <c r="D33" s="3">
-        <v>-1620023</v>
-      </c>
-      <c r="E33" s="8">
-        <v>7429167</v>
-      </c>
-      <c r="F33" s="8">
-        <v>35147941</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-1278407</v>
+      </c>
+      <c r="D33" s="7">
+        <v>72646</v>
+      </c>
+      <c r="E33" s="7">
+        <v>4309167</v>
+      </c>
+      <c r="F33" s="7">
+        <v>24628929</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="7">
-        <v>-0.8681120373522219</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-0.7346923148000198</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-0.3103641573569917</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.3367061048262329</v>
-      </c>
-      <c r="F34" s="7">
-        <v>0.4930475659558136</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="4">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4">
-        <v>0</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
+        <v>-0.87162038398318686</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-0.60745111884147773</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1.1123370715429064E-2</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.24223435414470584</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0.43348907702589273</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B36" s="3">
-        <v>-719177</v>
+        <v>-723295</v>
       </c>
       <c r="C36" s="3">
-        <v>-2158343</v>
+        <v>-2001702</v>
       </c>
       <c r="D36" s="3">
-        <v>-3778366</v>
+        <v>-1929056</v>
       </c>
       <c r="E36" s="3">
-        <v>3650801</v>
+        <v>2380111</v>
       </c>
       <c r="F36" s="3">
-        <v>38798742</v>
+        <v>27009040</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>